--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488123_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488123_PROCESSED_CHRONO.xlsx
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>H. HERNANDEZ CASTANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4306</v>
+        <v>-0.1682</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1968</v>
+        <v>0.0512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2338</v>
+        <v>-0.2193</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.1356</v>
+        <v>0.2829</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0941</v>
+        <v>0.1108</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.0415</v>
+        <v>0.172</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.4886</v>
+        <v>0.1059</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1322</v>
+        <v>0.0644</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6208</v>
+        <v>0.0415</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.647</v>
+        <v>0.177</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2263</v>
+        <v>0.0464</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4207</v>
+        <v>0.1306</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3706</v>
+        <v>0.3706</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.4823</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1117</v>
+        <v>0.3706</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3063</v>
+        <v>-0.1928</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5383</v>
+        <v>-0.0547</v>
       </c>
       <c r="U3" t="n">
-        <v>0.768</v>
+        <v>-0.138</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6304999999999999</v>
+        <v>-0.6289</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0011</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. HERNANDEZ CASTANO</t>
+          <t>D. RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.242</v>
+        <v>-0.266</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0512</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2932</v>
+        <v>-0.7786</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2829</v>
+        <v>0.5622</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1108</v>
+        <v>0.4132</v>
       </c>
       <c r="I4" t="n">
-        <v>0.172</v>
+        <v>0.149</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1059</v>
+        <v>0.4924</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0644</v>
+        <v>0.4509</v>
       </c>
       <c r="L4" t="n">
         <v>0.0415</v>
       </c>
       <c r="M4" t="n">
-        <v>0.177</v>
+        <v>0.0699</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0464</v>
+        <v>-0.0377</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1306</v>
+        <v>0.1076</v>
       </c>
       <c r="P4" t="n">
         <v>0.3706</v>
@@ -766,28 +766,28 @@
         <v>0.3706</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2666</v>
+        <v>0.06</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0547</v>
+        <v>0.0202</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2119</v>
+        <v>0.0398</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6289</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GARCIA</t>
+          <t>G. PEREZ CABRERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7076</v>
+        <v>-0.704</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2188</v>
+        <v>2.7405</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9264</v>
+        <v>-3.4445</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5622</v>
+        <v>-4.5731</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4132</v>
+        <v>-2.2458</v>
       </c>
       <c r="I5" t="n">
-        <v>0.149</v>
+        <v>-2.3273</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4924</v>
+        <v>-2.6125</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4509</v>
+        <v>-1.4218</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0415</v>
+        <v>-1.1907</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0699</v>
+        <v>-1.9605</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0377</v>
+        <v>-0.824</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1076</v>
+        <v>-1.1366</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3706</v>
+        <v>2.2234</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3815</v>
+        <v>-0.3168</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2736</v>
+        <v>0.2441</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1079</v>
+        <v>-0.5609</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2589</v>
+        <v>2.5183</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>5.6648</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2589</v>
+        <v>-3.1466</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. PEREZ CABRERA</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9125</v>
+        <v>-0.9629</v>
       </c>
       <c r="E6" t="n">
-        <v>2.729</v>
+        <v>-0.5319</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.6415</v>
+        <v>-0.431</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.5731</v>
+        <v>-2.1356</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.2458</v>
+        <v>-0.0941</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3273</v>
+        <v>-2.0415</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.6125</v>
+        <v>-0.4886</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.4218</v>
+        <v>0.1322</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1907</v>
+        <v>-0.6208</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9605</v>
+        <v>-1.647</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.824</v>
+        <v>-0.2263</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1366</v>
+        <v>-1.4207</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6676</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-1.4823</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2234</v>
+        <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5253</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2326</v>
+        <v>0.8096</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7578</v>
+        <v>0.1032</v>
       </c>
       <c r="V6" t="n">
-        <v>2.5183</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>5.6648</v>
+        <v>0.6294</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.1466</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8401</v>
+        <v>-1.6196</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2571</v>
+        <v>3.4529</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.0971</v>
+        <v>-5.0725</v>
       </c>
       <c r="G7" t="n">
         <v>6.0635</v>
@@ -1000,13 +1000,13 @@
         <v>0.7411</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9946</v>
+        <v>-0.7741</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6566</v>
+        <v>-0.4607</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.338</v>
+        <v>-0.3134</v>
       </c>
       <c r="V7" t="n">
         <v>-2.8327</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.6776</v>
+        <v>-2.8564</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7466</v>
+        <v>-2.2455</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.931</v>
+        <v>-0.6109</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7099</v>
@@ -1078,13 +1078,13 @@
         <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4119</v>
+        <v>-0.5907</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.766</v>
+        <v>-0.2649</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6459</v>
+        <v>-0.3258</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6294</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7715</v>
+        <v>-3.9624</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1181</v>
+        <v>-1.1613</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6534</v>
+        <v>-2.8012</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6918</v>
@@ -1156,13 +1156,13 @@
         <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3268</v>
+        <v>0.1359</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1467</v>
+        <v>-0.1899</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4735</v>
+        <v>0.3258</v>
       </c>
       <c r="V9" t="n">
         <v>-3.7771</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. NDIAYE</t>
+          <t>T. GARRETT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8302</v>
+        <v>-3.9845</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1094</v>
+        <v>-3.8985</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2792</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6904</v>
+        <v>-3.0115</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4617</v>
+        <v>-3.0838</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2287</v>
+        <v>0.0723</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7483</v>
+        <v>-2.2143</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.8727</v>
+        <v>-2.8778</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1244</v>
+        <v>0.6635</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9421</v>
+        <v>-0.7973</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.589</v>
+        <v>-0.206</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3531</v>
+        <v>-0.5913</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.1499</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.891</v>
+        <v>-2.4087</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>2.0101</v>
+        <v>0.1949</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8454</v>
+        <v>0.4101</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1646</v>
+        <v>-0.2151</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3155</v>
+        <v>0.3144</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. GARRETT</t>
+          <t>F. NDIAYE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9643</v>
+        <v>-5.2707</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7799</v>
+        <v>-5.2298</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1845</v>
+        <v>-0.0409</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.0115</v>
+        <v>-2.6904</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.0838</v>
+        <v>-2.4617</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0723</v>
+        <v>-0.2287</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2143</v>
+        <v>-1.7483</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.8778</v>
+        <v>-1.8727</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6635</v>
+        <v>0.1244</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7973</v>
+        <v>-0.9421</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.206</v>
+        <v>-0.589</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5913</v>
+        <v>-0.3531</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.4823</v>
+        <v>-3.1499</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4087</v>
+        <v>-3.891</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7849</v>
+        <v>0.5695</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4713</v>
+        <v>0.725</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3136</v>
+        <v>-0.1555</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3144</v>
+        <v>-0.3155</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.669</v>
+        <v>-5.4414</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6422</v>
+        <v>-2.6854</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.0268</v>
+        <v>-2.756</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5167</v>
@@ -1390,13 +1390,13 @@
         <v>0.9264</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0406</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1604</v>
+        <v>0.1172</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.201</v>
+        <v>-0.9302</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2589</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.659599999999999</v>
+        <v>-8.060499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.8693</v>
+        <v>-5.2702</v>
       </c>
       <c r="F13" t="n">
         <v>-2.7904</v>
@@ -1468,10 +1468,10 @@
         <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4699</v>
+        <v>-0.8708</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1279</v>
+        <v>-0.5288</v>
       </c>
       <c r="U13" t="n">
         <v>-0.342</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-33.2217</v>
+        <v>-32.67449999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.1905</v>
+        <v>-13.6433</v>
       </c>
       <c r="F14" t="n">
         <v>-19.0313</v>
@@ -1513,13 +1513,13 @@
         <v>-11.3586</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.020799999999999</v>
+        <v>-6.0208</v>
       </c>
       <c r="I14" t="n">
         <v>-5.338</v>
       </c>
       <c r="J14" t="n">
-        <v>1.472</v>
+        <v>1.471999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>-1.2915</v>
@@ -1546,19 +1546,19 @@
         <v>12.0435</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.2321</v>
+        <v>-1.6851</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2799</v>
+        <v>0.8271999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.512</v>
+        <v>-2.5121</v>
       </c>
       <c r="V14" t="n">
         <v>-9.440399999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>6.291999999999999</v>
+        <v>6.292</v>
       </c>
       <c r="X14" t="n">
         <v>-15.7325</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.7988</v>
+        <v>9.120699999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2082</v>
+        <v>4.5227</v>
       </c>
       <c r="F15" t="n">
-        <v>4.5906</v>
+        <v>4.598</v>
       </c>
       <c r="G15" t="n">
         <v>5.3861</v>
@@ -1624,13 +1624,13 @@
         <v>2.9646</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4862</v>
+        <v>-0.1918</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3756</v>
+        <v>-0.3099</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1106</v>
+        <v>0.1181</v>
       </c>
       <c r="V15" t="n">
         <v>1.8883</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1561</v>
+        <v>5.9586</v>
       </c>
       <c r="E16" t="n">
-        <v>4.2859</v>
+        <v>4.3838</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8702</v>
+        <v>1.5748</v>
       </c>
       <c r="G16" t="n">
         <v>2.8758</v>
@@ -1702,13 +1702,13 @@
         <v>2.0382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9272</v>
+        <v>0.7296</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5609</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3663</v>
+        <v>0.0709</v>
       </c>
       <c r="V16" t="n">
         <v>0.315</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8305</v>
+        <v>4.9956</v>
       </c>
       <c r="E17" t="n">
-        <v>5.0896</v>
+        <v>4.6979</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7409</v>
+        <v>0.2977</v>
       </c>
       <c r="G17" t="n">
         <v>0.1292</v>
@@ -1780,13 +1780,13 @@
         <v>2.594</v>
       </c>
       <c r="S17" t="n">
-        <v>1.831</v>
+        <v>0.9961</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6156</v>
+        <v>0.2239</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2154</v>
+        <v>0.7722</v>
       </c>
       <c r="V17" t="n">
         <v>2.2027</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRÍGUEZ</t>
+          <t>D. POL RUBIO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5324</v>
+        <v>3.2507</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5324</v>
+        <v>3.9922</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.7415</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5324</v>
+        <v>-1.5076</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2883</v>
+        <v>-1.5889</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2441</v>
+        <v>0.0813</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5324</v>
+        <v>0.8244</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2883</v>
+        <v>-0.524</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2441</v>
+        <v>1.3484</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-2.332</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-1.0648</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-1.2671</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.573</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.6501</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.0771</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4338</v>
+        <v>2.6062</v>
       </c>
       <c r="E19" t="n">
         <v>3.4603</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0265</v>
+        <v>-0.8542</v>
       </c>
       <c r="G19" t="n">
         <v>1.8664</v>
@@ -1936,13 +1936,13 @@
         <v>1.4823</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.007</v>
+        <v>0.1654</v>
       </c>
       <c r="T19" t="n">
         <v>0.531</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.538</v>
+        <v>-0.3656</v>
       </c>
       <c r="V19" t="n">
         <v>0.945</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. POL RUBIO</t>
+          <t>M. RAMOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3447</v>
+        <v>2.5324</v>
       </c>
       <c r="E20" t="n">
-        <v>3.1108</v>
+        <v>2.5324</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7661</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5076</v>
+        <v>2.5324</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5889</v>
+        <v>1.2883</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0813</v>
+        <v>1.2441</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8244</v>
+        <v>2.5324</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.524</v>
+        <v>1.2883</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3484</v>
+        <v>1.2441</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.332</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0648</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2671</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.333</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2313</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1017</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRIGUEZ</t>
+          <t>A. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.9739</v>
+        <v>2.4148</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3391</v>
+        <v>0.7396</v>
       </c>
       <c r="F21" t="n">
-        <v>4.313</v>
+        <v>1.6751</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7339</v>
+        <v>4.0654</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8536</v>
+        <v>1.9179</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8803</v>
+        <v>2.1475</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0881</v>
+        <v>2.5648</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.07779999999999999</v>
+        <v>1.1548</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1659</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6459</v>
+        <v>1.5006</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9314</v>
+        <v>0.7632</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7144</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1853</v>
+        <v>1.4823</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>2.594</v>
+        <v>2.4087</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2042</v>
+        <v>0.0159</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2773</v>
+        <v>-0.2676</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0731</v>
+        <v>0.2835</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6294</v>
+        <v>-3.1488</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6294</v>
+        <v>-0.6311</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5768</v>
+        <v>2.3212</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8026</v>
+        <v>-0.5088</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3793</v>
+        <v>2.83</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1552</v>
@@ -2170,13 +2170,13 @@
         <v>3.1499</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3236</v>
+        <v>-0.5792</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4414</v>
+        <v>-0.1476</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8822</v>
+        <v>-0.4315</v>
       </c>
       <c r="V22" t="n">
         <v>2.8321</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. LLANO ABASCAL</t>
+          <t>M. RAMOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.1566</v>
+        <v>1.9567</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1417</v>
+        <v>-2.3391</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2983</v>
+        <v>4.2958</v>
       </c>
       <c r="G23" t="n">
-        <v>4.0654</v>
+        <v>1.7339</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9179</v>
+        <v>0.8536</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1475</v>
+        <v>0.8803</v>
       </c>
       <c r="J23" t="n">
-        <v>2.5648</v>
+        <v>0.0881</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1548</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>1.41</v>
+        <v>0.1659</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5006</v>
+        <v>1.6459</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7632</v>
+        <v>0.9314</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.7144</v>
       </c>
       <c r="P23" t="n">
-        <v>1.4823</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4087</v>
+        <v>2.594</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2423</v>
+        <v>-0.2214</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.149</v>
+        <v>-0.2773</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.09329999999999999</v>
+        <v>0.0559</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.1488</v>
+        <v>0.6294</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6311</v>
+        <v>0.6294</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.5177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9363</v>
+        <v>1.1579</v>
       </c>
       <c r="E24" t="n">
         <v>-0.1209</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0572</v>
+        <v>1.2788</v>
       </c>
       <c r="G24" t="n">
         <v>0.8374</v>
@@ -2326,13 +2326,13 @@
         <v>1.6676</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3447</v>
+        <v>-0.1231</v>
       </c>
       <c r="T24" t="n">
         <v>0.2363</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.581</v>
+        <v>-0.3594</v>
       </c>
       <c r="V24" t="n">
         <v>0.6289</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1089</v>
+        <v>-0.9356</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2396</v>
+        <v>-2.4148</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3486</v>
+        <v>1.4792</v>
       </c>
       <c r="G25" t="n">
         <v>-3.4985</v>
@@ -2404,13 +2404,13 @@
         <v>1.1117</v>
       </c>
       <c r="S25" t="n">
-        <v>2.4597</v>
+        <v>1.4152</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3254</v>
+        <v>1.1503</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1343</v>
+        <v>0.2649</v>
       </c>
       <c r="V25" t="n">
         <v>1.8888</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.627</v>
+        <v>-1.5044</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0121</v>
+        <v>0.0858</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6149</v>
+        <v>-1.5902</v>
       </c>
       <c r="G26" t="n">
         <v>-0.9068000000000001</v>
@@ -2482,13 +2482,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.0172</v>
+        <v>0.1054</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0336</v>
+        <v>0.0644</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V26" t="n">
         <v>-1.2589</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>33.22179999999999</v>
+        <v>33.8748</v>
       </c>
       <c r="E27" t="n">
-        <v>19.0312</v>
+        <v>19.0311</v>
       </c>
       <c r="F27" t="n">
-        <v>14.1906</v>
+        <v>14.8435</v>
       </c>
       <c r="G27" t="n">
         <v>11.3585</v>
@@ -2536,10 +2536,10 @@
         <v>12.8305</v>
       </c>
       <c r="K27" t="n">
-        <v>4.729199999999999</v>
+        <v>4.729200000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>8.1012</v>
+        <v>8.101200000000002</v>
       </c>
       <c r="M27" t="n">
         <v>-1.4719</v>
@@ -2560,16 +2560,16 @@
         <v>22.2345</v>
       </c>
       <c r="S27" t="n">
-        <v>2.2321</v>
+        <v>2.8851</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5122</v>
+        <v>2.5124</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2800999999999998</v>
+        <v>0.3729000000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>9.440200000000001</v>
+        <v>9.440199999999999</v>
       </c>
       <c r="W27" t="n">
         <v>15.7324</v>
